--- a/reports/Debug-purgatory-20260106/purgatory_Report_20260106.xlsx
+++ b/reports/Debug-purgatory-20260106/purgatory_Report_20260106.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
   <si>
     <t>purgatory Resort
 Daily Management Report
@@ -560,6 +560,15 @@
   </si>
   <si>
     <t>PR % of IT Services</t>
+  </si>
+  <si>
+    <t>Durango Mountain Realty - Revenue</t>
+  </si>
+  <si>
+    <t>Durango Mountain Realty - Payroll</t>
+  </si>
+  <si>
+    <t>PR % of Durango Mountain Realty</t>
   </si>
   <si>
     <t>Pass-through Accounts - Revenue</t>
@@ -962,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N178"/>
+  <dimension ref="A1:N181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1219,7 +1228,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="4">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C9" s="4">
         <v>1130</v>
@@ -1228,7 +1237,7 @@
         <v>1069</v>
       </c>
       <c r="E9" s="4">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="F9" s="4">
         <v>6506</v>
@@ -1240,7 +1249,7 @@
         <v>6383</v>
       </c>
       <c r="I9" s="4">
-        <v>7835</v>
+        <v>7834</v>
       </c>
       <c r="J9" s="4">
         <v>9602</v>
@@ -1249,7 +1258,7 @@
         <v>10142</v>
       </c>
       <c r="L9" s="4">
-        <v>29760</v>
+        <v>29759</v>
       </c>
       <c r="M9" s="4">
         <v>42392</v>
@@ -1307,7 +1316,7 @@
         <v>22</v>
       </c>
       <c r="B11" s="4">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="C11" s="4">
         <v>2275</v>
@@ -1316,7 +1325,7 @@
         <v>2293</v>
       </c>
       <c r="E11" s="4">
-        <v>4882</v>
+        <v>4881</v>
       </c>
       <c r="F11" s="4">
         <v>18411</v>
@@ -1328,7 +1337,7 @@
         <v>19349</v>
       </c>
       <c r="I11" s="4">
-        <v>17737</v>
+        <v>17736</v>
       </c>
       <c r="J11" s="4">
         <v>23576</v>
@@ -1337,7 +1346,7 @@
         <v>26624</v>
       </c>
       <c r="L11" s="4">
-        <v>71752</v>
+        <v>71751</v>
       </c>
       <c r="M11" s="4">
         <v>105109</v>
@@ -1400,7 +1409,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="4">
-        <v>0</v>
+        <v>297.92</v>
       </c>
       <c r="C15" s="4">
         <v>377.99</v>
@@ -1409,7 +1418,7 @@
         <v>290.04</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>595.84</v>
       </c>
       <c r="F15" s="4">
         <v>2485.93</v>
@@ -1421,7 +1430,7 @@
         <v>2030.28</v>
       </c>
       <c r="I15" s="4">
-        <v>0</v>
+        <v>1787.52</v>
       </c>
       <c r="J15" s="4">
         <v>2107.94</v>
@@ -1430,7 +1439,7 @@
         <v>1740.24</v>
       </c>
       <c r="L15" s="4">
-        <v>0</v>
+        <v>19960.64</v>
       </c>
       <c r="M15" s="4">
         <v>23725.33</v>
@@ -1532,7 +1541,7 @@
         <v>28</v>
       </c>
       <c r="B18" s="4">
-        <v>271.4433333333333</v>
+        <v>3184.8209</v>
       </c>
       <c r="C18" s="4">
         <v>3944.97</v>
@@ -1541,7 +1550,7 @@
         <v>4414.37</v>
       </c>
       <c r="E18" s="4">
-        <v>720.1819444444444</v>
+        <v>6784.247969444445</v>
       </c>
       <c r="F18" s="4">
         <v>32142.69</v>
@@ -1553,7 +1562,7 @@
         <v>37040.2</v>
       </c>
       <c r="I18" s="4">
-        <v>2363.423749999999</v>
+        <v>24917.81513888889</v>
       </c>
       <c r="J18" s="4">
         <v>33268.82</v>
@@ -1562,7 +1571,7 @@
         <v>34660.68</v>
       </c>
       <c r="L18" s="4">
-        <v>9649.494444444443</v>
+        <v>165674.543802778</v>
       </c>
       <c r="M18" s="4">
         <v>200305.79</v>
@@ -1664,7 +1673,7 @@
         <v>31</v>
       </c>
       <c r="B21" s="4">
-        <v>0</v>
+        <v>1631.281094444445</v>
       </c>
       <c r="C21" s="4">
         <v>1780.56</v>
@@ -1673,7 +1682,7 @@
         <v>1815.49</v>
       </c>
       <c r="E21" s="4">
-        <v>0</v>
+        <v>4095.973080555555</v>
       </c>
       <c r="F21" s="4">
         <v>14457.75</v>
@@ -1685,7 +1694,7 @@
         <v>14997.24</v>
       </c>
       <c r="I21" s="4">
-        <v>0</v>
+        <v>11315.78621111111</v>
       </c>
       <c r="J21" s="4">
         <v>12077.19</v>
@@ -1694,7 +1703,7 @@
         <v>13026.4</v>
       </c>
       <c r="L21" s="4">
-        <v>875.1436111111111</v>
+        <v>121340.0536722222</v>
       </c>
       <c r="M21" s="4">
         <v>137868.71</v>
@@ -1796,7 +1805,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="4">
-        <v>0</v>
+        <v>1512.5606</v>
       </c>
       <c r="C24" s="4">
         <v>236.9</v>
@@ -1805,7 +1814,7 @@
         <v>2015.82</v>
       </c>
       <c r="E24" s="4">
-        <v>0</v>
+        <v>4262.10108888889</v>
       </c>
       <c r="F24" s="4">
         <v>947.6</v>
@@ -1817,7 +1826,7 @@
         <v>5953.26</v>
       </c>
       <c r="I24" s="4">
-        <v>0</v>
+        <v>11789.17196388889</v>
       </c>
       <c r="J24" s="4">
         <v>7896</v>
@@ -1826,7 +1835,7 @@
         <v>6826.16</v>
       </c>
       <c r="L24" s="4">
-        <v>1228.501388888889</v>
+        <v>109442.3241666667</v>
       </c>
       <c r="M24" s="4">
         <v>119632.4</v>
@@ -1928,7 +1937,7 @@
         <v>37</v>
       </c>
       <c r="B27" s="4">
-        <v>0</v>
+        <v>653.3747222222222</v>
       </c>
       <c r="C27" s="4">
         <v>1112</v>
@@ -1937,7 +1946,7 @@
         <v>785.03</v>
       </c>
       <c r="E27" s="4">
-        <v>0</v>
+        <v>1513.406388888889</v>
       </c>
       <c r="F27" s="4">
         <v>5690.3</v>
@@ -1949,7 +1958,7 @@
         <v>5422.13</v>
       </c>
       <c r="I27" s="4">
-        <v>0</v>
+        <v>4077.73611111111</v>
       </c>
       <c r="J27" s="4">
         <v>4779.9</v>
@@ -1958,7 +1967,7 @@
         <v>4371.36</v>
       </c>
       <c r="L27" s="4">
-        <v>0</v>
+        <v>41192.55944444444</v>
       </c>
       <c r="M27" s="4">
         <v>41883.4</v>
@@ -2060,7 +2069,7 @@
         <v>40</v>
       </c>
       <c r="B30" s="4">
-        <v>97.60391666666668</v>
+        <v>1642.975027777778</v>
       </c>
       <c r="C30" s="4">
         <v>2383.57</v>
@@ -2069,7 +2078,7 @@
         <v>1954.26</v>
       </c>
       <c r="E30" s="4">
-        <v>308.8389166666667</v>
+        <v>3516.907805555556</v>
       </c>
       <c r="F30" s="4">
         <v>16444.3</v>
@@ -2081,7 +2090,7 @@
         <v>13956.5</v>
       </c>
       <c r="I30" s="4">
-        <v>642.3650972222223</v>
+        <v>10689.92231944445</v>
       </c>
       <c r="J30" s="4">
         <v>14060.73</v>
@@ -2090,7 +2099,7 @@
         <v>14035.33</v>
       </c>
       <c r="L30" s="4">
-        <v>15408.65602777778</v>
+        <v>137382.6724722221</v>
       </c>
       <c r="M30" s="4">
         <v>129472.1</v>
@@ -2192,7 +2201,7 @@
         <v>43</v>
       </c>
       <c r="B33" s="4">
-        <v>0</v>
+        <v>919.1625694444444</v>
       </c>
       <c r="C33" s="4">
         <v>1966.5</v>
@@ -2201,7 +2210,7 @@
         <v>748.99</v>
       </c>
       <c r="E33" s="4">
-        <v>0</v>
+        <v>1812.765138888889</v>
       </c>
       <c r="F33" s="4">
         <v>9177.690000000001</v>
@@ -2213,7 +2222,7 @@
         <v>6189.67</v>
       </c>
       <c r="I33" s="4">
-        <v>0</v>
+        <v>7944.304172222224</v>
       </c>
       <c r="J33" s="4">
         <v>7283.19</v>
@@ -2222,7 +2231,7 @@
         <v>5389.44</v>
       </c>
       <c r="L33" s="4">
-        <v>0</v>
+        <v>81828.90503055557</v>
       </c>
       <c r="M33" s="4">
         <v>88979.10000000001</v>
@@ -2324,7 +2333,7 @@
         <v>46</v>
       </c>
       <c r="B36" s="4">
-        <v>0</v>
+        <v>3274.182158333333</v>
       </c>
       <c r="C36" s="4">
         <v>3983.6</v>
@@ -2333,7 +2342,7 @@
         <v>3957.53</v>
       </c>
       <c r="E36" s="4">
-        <v>0</v>
+        <v>6586.353875000001</v>
       </c>
       <c r="F36" s="4">
         <v>30380.38</v>
@@ -2345,7 +2354,7 @@
         <v>29999.4</v>
       </c>
       <c r="I36" s="4">
-        <v>0</v>
+        <v>23416.53548333333</v>
       </c>
       <c r="J36" s="4">
         <v>27669.86</v>
@@ -2354,7 +2363,7 @@
         <v>28343.32</v>
       </c>
       <c r="L36" s="4">
-        <v>419.7450333333333</v>
+        <v>165808.9219361112</v>
       </c>
       <c r="M36" s="4">
         <v>217698.07</v>
@@ -2456,7 +2465,7 @@
         <v>49</v>
       </c>
       <c r="B39" s="4">
-        <v>120.5916666666667</v>
+        <v>3737.325961111111</v>
       </c>
       <c r="C39" s="4">
         <v>1006.39</v>
@@ -2465,7 +2474,7 @@
         <v>1215.14</v>
       </c>
       <c r="E39" s="4">
-        <v>286.9041666666667</v>
+        <v>7567.80908888889</v>
       </c>
       <c r="F39" s="4">
         <v>7543.03</v>
@@ -2477,7 +2486,7 @@
         <v>8242.940000000001</v>
       </c>
       <c r="I39" s="4">
-        <v>1112.063194444444</v>
+        <v>27192.87918333334</v>
       </c>
       <c r="J39" s="4">
         <v>7909.38</v>
@@ -2486,7 +2495,7 @@
         <v>8698.610000000001</v>
       </c>
       <c r="L39" s="4">
-        <v>6450.651250000001</v>
+        <v>180599.9492555556</v>
       </c>
       <c r="M39" s="4">
         <v>50045.08</v>
@@ -2500,7 +2509,7 @@
         <v>50</v>
       </c>
       <c r="B40" s="5">
-        <v>0.1492471306824006</v>
+        <v>4.625403989667711</v>
       </c>
       <c r="C40" s="5">
         <v>0.5776783642723047</v>
@@ -2509,7 +2518,7 @@
         <v>84.72716116526517</v>
       </c>
       <c r="E40" s="5">
-        <v>0.1660963375257046</v>
+        <v>4.381202919993089</v>
       </c>
       <c r="F40" s="5">
         <v>0.6114000207208908</v>
@@ -2521,7 +2530,7 @@
         <v>2.49007798051786</v>
       </c>
       <c r="I40" s="5">
-        <v>0.1259654649784815</v>
+        <v>3.080187967324528</v>
       </c>
       <c r="J40" s="5">
         <v>0.5100151747534074</v>
@@ -2530,7 +2539,7 @@
         <v>1.725423484600059</v>
       </c>
       <c r="L40" s="5">
-        <v>0.249530390599653</v>
+        <v>6.986143589767979</v>
       </c>
       <c r="M40" s="5">
         <v>0.8192075396215449</v>
@@ -2720,7 +2729,7 @@
         <v>55</v>
       </c>
       <c r="B45" s="4">
-        <v>345</v>
+        <v>4660.749444444444</v>
       </c>
       <c r="C45" s="4">
         <v>6095.92</v>
@@ -2729,7 +2738,7 @@
         <v>4834.11</v>
       </c>
       <c r="E45" s="4">
-        <v>830</v>
+        <v>10020.05944444445</v>
       </c>
       <c r="F45" s="4">
         <v>34935.56</v>
@@ -2741,7 +2750,7 @@
         <v>43706.53</v>
       </c>
       <c r="I45" s="4">
-        <v>4350.903194444444</v>
+        <v>34809.19547222221</v>
       </c>
       <c r="J45" s="4">
         <v>49943.41</v>
@@ -2750,7 +2759,7 @@
         <v>58362.76</v>
       </c>
       <c r="L45" s="4">
-        <v>20562.96930555556</v>
+        <v>212802.9865499998</v>
       </c>
       <c r="M45" s="4">
         <v>244214.23</v>
@@ -2764,7 +2773,7 @@
         <v>56</v>
       </c>
       <c r="B46" s="5">
-        <v>1.734781565859097</v>
+        <v>23.43589049075434</v>
       </c>
       <c r="C46" s="5">
         <v>22.95582752777255</v>
@@ -2773,7 +2782,7 @@
         <v>30.5818904163319</v>
       </c>
       <c r="E46" s="5">
-        <v>1.617790865640909</v>
+        <v>19.53055499084476</v>
       </c>
       <c r="F46" s="5">
         <v>22.84998107802043</v>
@@ -2785,7 +2794,7 @@
         <v>34.64429312619617</v>
       </c>
       <c r="I46" s="5">
-        <v>2.172539416761025</v>
+        <v>17.38129897390154</v>
       </c>
       <c r="J46" s="5">
         <v>19.8705399770832</v>
@@ -2794,7 +2803,7 @@
         <v>19.34659276900594</v>
       </c>
       <c r="L46" s="5">
-        <v>2.732663502048399</v>
+        <v>28.279911613493</v>
       </c>
       <c r="M46" s="5">
         <v>22.2919216464712</v>
@@ -2852,7 +2861,7 @@
         <v>58</v>
       </c>
       <c r="B48" s="4">
-        <v>0</v>
+        <v>291.4466666666667</v>
       </c>
       <c r="C48" s="4">
         <v>266.97</v>
@@ -2861,7 +2870,7 @@
         <v>339.2</v>
       </c>
       <c r="E48" s="4">
-        <v>0</v>
+        <v>708.165</v>
       </c>
       <c r="F48" s="4">
         <v>1962.54</v>
@@ -2873,7 +2882,7 @@
         <v>2414.5</v>
       </c>
       <c r="I48" s="4">
-        <v>0</v>
+        <v>2087.48</v>
       </c>
       <c r="J48" s="4">
         <v>2606.82</v>
@@ -2882,7 +2891,7 @@
         <v>1977.24</v>
       </c>
       <c r="L48" s="4">
-        <v>811.51125</v>
+        <v>13095.40083333333</v>
       </c>
       <c r="M48" s="4">
         <v>15371.76</v>
@@ -2896,7 +2905,7 @@
         <v>59</v>
       </c>
       <c r="B49" s="5">
-        <v>0</v>
+        <v>45.53854166666667</v>
       </c>
       <c r="C49" s="5">
         <v>43.46275946275946</v>
@@ -2905,7 +2914,7 @@
         <v>106</v>
       </c>
       <c r="E49" s="5">
-        <v>0</v>
+        <v>49.17812499999999</v>
       </c>
       <c r="F49" s="5">
         <v>39.48002100193725</v>
@@ -2917,7 +2926,7 @@
         <v>63.80813953488372</v>
       </c>
       <c r="I49" s="5">
-        <v>0</v>
+        <v>33.45320512820513</v>
       </c>
       <c r="J49" s="5">
         <v>40.952192436753</v>
@@ -2926,7 +2935,7 @@
         <v>24.23088235294118</v>
       </c>
       <c r="L49" s="5">
-        <v>3.820674435028248</v>
+        <v>61.65442953546767</v>
       </c>
       <c r="M49" s="5">
         <v>54.16514708012106</v>
@@ -3014,7 +3023,7 @@
         <v>10365.99</v>
       </c>
       <c r="L51" s="4">
-        <v>0</v>
+        <v>7000.417127777776</v>
       </c>
       <c r="M51" s="4">
         <v>76968.98</v>
@@ -3058,7 +3067,7 @@
         <v>4.361673734792562</v>
       </c>
       <c r="L52" s="5">
-        <v>0</v>
+        <v>0.8057004847631409</v>
       </c>
       <c r="M52" s="5">
         <v>7.134179596476482</v>
@@ -3380,7 +3389,7 @@
         <v>70</v>
       </c>
       <c r="B60" s="4">
-        <v>0</v>
+        <v>74.11499999999999</v>
       </c>
       <c r="C60" s="4">
         <v>579.26</v>
@@ -3389,7 +3398,7 @@
         <v>1614.52</v>
       </c>
       <c r="E60" s="4">
-        <v>73.625</v>
+        <v>220.18</v>
       </c>
       <c r="F60" s="4">
         <v>3774.8</v>
@@ -3401,7 +3410,7 @@
         <v>10632.17</v>
       </c>
       <c r="I60" s="4">
-        <v>99.675</v>
+        <v>394.32</v>
       </c>
       <c r="J60" s="4">
         <v>3612.04</v>
@@ -3410,7 +3419,7 @@
         <v>8272.42</v>
       </c>
       <c r="L60" s="4">
-        <v>303.5833333333333</v>
+        <v>9155.92882222222</v>
       </c>
       <c r="M60" s="4">
         <v>25559.22</v>
@@ -3424,7 +3433,7 @@
         <v>71</v>
       </c>
       <c r="B61" s="5">
-        <v>0</v>
+        <v>0.805044795314523</v>
       </c>
       <c r="C61" s="5">
         <v>5.100556494787265</v>
@@ -3433,7 +3442,7 @@
         <v>16.88869083670423</v>
       </c>
       <c r="E61" s="5">
-        <v>0.3043140049335035</v>
+        <v>0.910069373259882</v>
       </c>
       <c r="F61" s="5">
         <v>4.107167163379144</v>
@@ -3445,7 +3454,7 @@
         <v>16.21468002902492</v>
       </c>
       <c r="I61" s="5">
-        <v>0.1226310552889817</v>
+        <v>0.4851354674848386</v>
       </c>
       <c r="J61" s="5">
         <v>3.069079090192965</v>
@@ -3454,7 +3463,7 @@
         <v>10.15934951042453</v>
       </c>
       <c r="L61" s="5">
-        <v>0.09027337871613719</v>
+        <v>2.722602130331472</v>
       </c>
       <c r="M61" s="5">
         <v>4.87117270372229</v>
@@ -3521,7 +3530,7 @@
         <v>507.92</v>
       </c>
       <c r="E63" s="4">
-        <v>0</v>
+        <v>183.95</v>
       </c>
       <c r="F63" s="4">
         <v>4284.8</v>
@@ -3533,7 +3542,7 @@
         <v>4014.51</v>
       </c>
       <c r="I63" s="4">
-        <v>0</v>
+        <v>866.6966666666667</v>
       </c>
       <c r="J63" s="4">
         <v>4591.04</v>
@@ -3542,7 +3551,7 @@
         <v>3641.64</v>
       </c>
       <c r="L63" s="4">
-        <v>135.0833333333333</v>
+        <v>16013.32375</v>
       </c>
       <c r="M63" s="4">
         <v>29837.6</v>
@@ -3565,7 +3574,7 @@
         <v>58.11973636030758</v>
       </c>
       <c r="E64" s="5">
-        <v>0</v>
+        <v>6.237919224117467</v>
       </c>
       <c r="F64" s="5">
         <v>16.49539781942606</v>
@@ -3577,7 +3586,7 @@
         <v>32.96607733808519</v>
       </c>
       <c r="I64" s="5">
-        <v>0</v>
+        <v>3.482670429963645</v>
       </c>
       <c r="J64" s="5">
         <v>12.96044684498724</v>
@@ -3586,7 +3595,7 @@
         <v>12.95723972836208</v>
       </c>
       <c r="L64" s="5">
-        <v>0.103164039172143</v>
+        <v>12.22948174179796</v>
       </c>
       <c r="M64" s="5">
         <v>17.53831893094642</v>
@@ -3776,7 +3785,7 @@
         <v>79</v>
       </c>
       <c r="B69" s="4">
-        <v>80.38166666666667</v>
+        <v>1290.981666666667</v>
       </c>
       <c r="C69" s="4">
         <v>1066.11</v>
@@ -3785,7 +3794,7 @@
         <v>1553.26</v>
       </c>
       <c r="E69" s="4">
-        <v>80.38166666666667</v>
+        <v>2501.581666666666</v>
       </c>
       <c r="F69" s="4">
         <v>7462.77</v>
@@ -3797,7 +3806,7 @@
         <v>11851.29</v>
       </c>
       <c r="I69" s="4">
-        <v>343.2038888888889</v>
+        <v>7606.80388888889</v>
       </c>
       <c r="J69" s="4">
         <v>6396.66</v>
@@ -3806,7 +3815,7 @@
         <v>10466.17</v>
       </c>
       <c r="L69" s="4">
-        <v>1434.780555555556</v>
+        <v>82544.98055555555</v>
       </c>
       <c r="M69" s="4">
         <v>71429.37</v>
@@ -3908,7 +3917,7 @@
         <v>82</v>
       </c>
       <c r="B72" s="4">
-        <v>286.575</v>
+        <v>643.3270333333334</v>
       </c>
       <c r="C72" s="4">
         <v>843</v>
@@ -3917,7 +3926,7 @@
         <v>784.86</v>
       </c>
       <c r="E72" s="4">
-        <v>433.0708333333334</v>
+        <v>1482.5788</v>
       </c>
       <c r="F72" s="4">
         <v>6390.74</v>
@@ -3929,7 +3938,7 @@
         <v>6365.54</v>
       </c>
       <c r="I72" s="4">
-        <v>1871.194111111111</v>
+        <v>5137.317744444446</v>
       </c>
       <c r="J72" s="4">
         <v>5590.24</v>
@@ -3938,7 +3947,7 @@
         <v>6116.48</v>
       </c>
       <c r="L72" s="4">
-        <v>9977.421230555556</v>
+        <v>30194.057675</v>
       </c>
       <c r="M72" s="4">
         <v>38846.58</v>
@@ -3952,7 +3961,7 @@
         <v>83</v>
       </c>
       <c r="B73" s="5">
-        <v>5.309274626085893</v>
+        <v>11.91869456286061</v>
       </c>
       <c r="C73" s="5">
         <v>18.68798382591578</v>
@@ -3961,7 +3970,7 @@
         <v>25.26858699256617</v>
       </c>
       <c r="E73" s="5">
-        <v>4.446362672815949</v>
+        <v>15.22172016316406</v>
       </c>
       <c r="F73" s="5">
         <v>17.50616205815755</v>
@@ -3973,7 +3982,7 @@
         <v>25.95253840364454</v>
       </c>
       <c r="I73" s="5">
-        <v>4.851154514919606</v>
+        <v>13.31872627353433</v>
       </c>
       <c r="J73" s="5">
         <v>11.95850768509702</v>
@@ -3982,7 +3991,7 @@
         <v>14.16326583540038</v>
       </c>
       <c r="L73" s="5">
-        <v>6.258105717790199</v>
+        <v>18.93852134863541</v>
       </c>
       <c r="M73" s="5">
         <v>18.63931661529728</v>
@@ -4040,7 +4049,7 @@
         <v>85</v>
       </c>
       <c r="B75" s="4">
-        <v>0</v>
+        <v>694.887761111111</v>
       </c>
       <c r="C75" s="4">
         <v>2126.25</v>
@@ -4049,7 +4058,7 @@
         <v>2470.27</v>
       </c>
       <c r="E75" s="4">
-        <v>174.3255555555556</v>
+        <v>2345.256588888889</v>
       </c>
       <c r="F75" s="4">
         <v>17513.87</v>
@@ -4061,7 +4070,7 @@
         <v>18995.44</v>
       </c>
       <c r="I75" s="4">
-        <v>884.5527777777778</v>
+        <v>9020.044466666668</v>
       </c>
       <c r="J75" s="4">
         <v>15352.6</v>
@@ -4070,7 +4079,7 @@
         <v>17770.75</v>
       </c>
       <c r="L75" s="4">
-        <v>3041.316111111111</v>
+        <v>28161.69359444442</v>
       </c>
       <c r="M75" s="4">
         <v>59628.14</v>
@@ -4084,7 +4093,7 @@
         <v>86</v>
       </c>
       <c r="B76" s="5">
-        <v>0</v>
+        <v>19.40143904063543</v>
       </c>
       <c r="C76" s="5">
         <v>32.41313812532013</v>
@@ -4093,7 +4102,7 @@
         <v>44.08810946934069</v>
       </c>
       <c r="E76" s="5">
-        <v>2.23346549661449</v>
+        <v>30.04751457867473</v>
       </c>
       <c r="F76" s="5">
         <v>32.99077724429462</v>
@@ -4105,7 +4114,7 @@
         <v>40.06782791419461</v>
       </c>
       <c r="I76" s="5">
-        <v>2.976119713884874</v>
+        <v>30.34836680385048</v>
       </c>
       <c r="J76" s="5">
         <v>22.58392884987099</v>
@@ -4114,7 +4123,7 @@
         <v>25.59859949735519</v>
       </c>
       <c r="L76" s="5">
-        <v>6.660723035167439</v>
+        <v>61.6763382630798</v>
       </c>
       <c r="M76" s="5">
         <v>25.37418299965221</v>
@@ -4304,7 +4313,7 @@
         <v>91</v>
       </c>
       <c r="B81" s="4">
-        <v>0</v>
+        <v>264.6051666666667</v>
       </c>
       <c r="C81" s="4">
         <v>169.03</v>
@@ -4313,7 +4322,7 @@
         <v>131.75</v>
       </c>
       <c r="E81" s="4">
-        <v>0</v>
+        <v>530.2504777777779</v>
       </c>
       <c r="F81" s="4">
         <v>1227.61</v>
@@ -4325,7 +4334,7 @@
         <v>1376.54</v>
       </c>
       <c r="I81" s="4">
-        <v>199.472</v>
+        <v>1755.098555555556</v>
       </c>
       <c r="J81" s="4">
         <v>1300.98</v>
@@ -4334,7 +4343,7 @@
         <v>1017.22</v>
       </c>
       <c r="L81" s="4">
-        <v>591.6668333333332</v>
+        <v>5441.237133333333</v>
       </c>
       <c r="M81" s="4">
         <v>9726.209999999999</v>
@@ -4348,7 +4357,7 @@
         <v>92</v>
       </c>
       <c r="B82" s="5">
-        <v>0</v>
+        <v>22.95923355025308</v>
       </c>
       <c r="C82" s="5">
         <v>17.54151100041511</v>
@@ -4357,7 +4366,7 @@
         <v>23.67858234036053</v>
       </c>
       <c r="E82" s="5">
-        <v>0</v>
+        <v>27.77663871689477</v>
       </c>
       <c r="F82" s="5">
         <v>15.74222256418148</v>
@@ -4369,7 +4378,7 @@
         <v>24.98897176954538</v>
       </c>
       <c r="I82" s="5">
-        <v>2.33762367999475</v>
+        <v>20.56809950364586</v>
       </c>
       <c r="J82" s="5">
         <v>13.02810448680396</v>
@@ -4378,7 +4387,7 @@
         <v>10.68659946526031</v>
       </c>
       <c r="L82" s="5">
-        <v>2.287336112413711</v>
+        <v>21.035382566844</v>
       </c>
       <c r="M82" s="5">
         <v>25.216432483332</v>
@@ -4436,7 +4445,7 @@
         <v>94</v>
       </c>
       <c r="B84" s="4">
-        <v>170.2888888888889</v>
+        <v>615.9333333333334</v>
       </c>
       <c r="C84" s="4">
         <v>569.9</v>
@@ -4445,7 +4454,7 @@
         <v>568.85</v>
       </c>
       <c r="E84" s="4">
-        <v>415.9111111111112</v>
+        <v>1246.948888888889</v>
       </c>
       <c r="F84" s="4">
         <v>3781.3</v>
@@ -4457,7 +4466,7 @@
         <v>4847.04</v>
       </c>
       <c r="I84" s="4">
-        <v>543.0388888888889</v>
+        <v>4667.460722222222</v>
       </c>
       <c r="J84" s="4">
         <v>3211.4</v>
@@ -4466,7 +4475,7 @@
         <v>3604.86</v>
       </c>
       <c r="L84" s="4">
-        <v>9669.726666666669</v>
+        <v>39701.54602777777</v>
       </c>
       <c r="M84" s="4">
         <v>27355.22</v>
@@ -4480,7 +4489,7 @@
         <v>95</v>
       </c>
       <c r="B85" s="5">
-        <v>50.68121693121693</v>
+        <v>183.3134920634921</v>
       </c>
       <c r="C85" s="5">
         <v>74.22892570594978</v>
@@ -4489,7 +4498,7 @@
         <v>227.54</v>
       </c>
       <c r="E85" s="5">
-        <v>38.19202122232426</v>
+        <v>114.5040302009999</v>
       </c>
       <c r="F85" s="5">
         <v>55.95153717648417</v>
@@ -4501,7 +4510,7 @@
         <v>403.92</v>
       </c>
       <c r="I85" s="5">
-        <v>13.07267426309314</v>
+        <v>112.3606336596587</v>
       </c>
       <c r="J85" s="5">
         <v>27.42229254601052</v>
@@ -4510,7 +4519,7 @@
         <v>87.92341463414634</v>
       </c>
       <c r="L85" s="5">
-        <v>48.96041823944432</v>
+        <v>201.0195701780487</v>
       </c>
       <c r="M85" s="5">
         <v>47.07976164803829</v>
@@ -4568,7 +4577,7 @@
         <v>97</v>
       </c>
       <c r="B87" s="4">
-        <v>239.3528111111111</v>
+        <v>1623.193111111111</v>
       </c>
       <c r="C87" s="4">
         <v>1424.78</v>
@@ -4577,7 +4586,7 @@
         <v>1871.96</v>
       </c>
       <c r="E87" s="4">
-        <v>510.0286</v>
+        <v>3293.030833333334</v>
       </c>
       <c r="F87" s="4">
         <v>9542.91</v>
@@ -4589,7 +4598,7 @@
         <v>13109.95</v>
       </c>
       <c r="I87" s="4">
-        <v>1461.137622222222</v>
+        <v>10358.19685555556</v>
       </c>
       <c r="J87" s="4">
         <v>8585.48</v>
@@ -4598,7 +4607,7 @@
         <v>12946.87</v>
       </c>
       <c r="L87" s="4">
-        <v>7463.975311111111</v>
+        <v>53972.64846111111</v>
       </c>
       <c r="M87" s="4">
         <v>51852.01</v>
@@ -4612,7 +4621,7 @@
         <v>98</v>
       </c>
       <c r="B88" s="5">
-        <v>5.277528622260638</v>
+        <v>35.79004593085187</v>
       </c>
       <c r="C88" s="5">
         <v>33.86833760417608</v>
@@ -4621,7 +4630,7 @@
         <v>51.22608645681402</v>
       </c>
       <c r="E88" s="5">
-        <v>5.109974511674134</v>
+        <v>32.99286280120442</v>
       </c>
       <c r="F88" s="5">
         <v>28.0304316486326</v>
@@ -4633,7 +4642,7 @@
         <v>47.5300417475605</v>
       </c>
       <c r="I88" s="5">
-        <v>3.955733587410155</v>
+        <v>28.04271588340201</v>
       </c>
       <c r="J88" s="5">
         <v>19.69339206078392</v>
@@ -4642,7 +4651,7 @@
         <v>33.11066674407144</v>
       </c>
       <c r="L88" s="5">
-        <v>6.073647047607909</v>
+        <v>43.91906501746025</v>
       </c>
       <c r="M88" s="5">
         <v>30.66495304422578</v>
@@ -4700,7 +4709,7 @@
         <v>100</v>
       </c>
       <c r="B90" s="4">
-        <v>237.5544166666667</v>
+        <v>2210.239166666667</v>
       </c>
       <c r="C90" s="4">
         <v>2661.1</v>
@@ -4709,7 +4718,7 @@
         <v>2422.21</v>
       </c>
       <c r="E90" s="4">
-        <v>654.8255277777778</v>
+        <v>4506.670911111111</v>
       </c>
       <c r="F90" s="4">
         <v>20377.3</v>
@@ -4721,7 +4730,7 @@
         <v>17186.04</v>
       </c>
       <c r="I90" s="4">
-        <v>3310.257180555555</v>
+        <v>15590.547825</v>
       </c>
       <c r="J90" s="4">
         <v>20510.2</v>
@@ -4730,7 +4739,7 @@
         <v>18785.33</v>
       </c>
       <c r="L90" s="4">
-        <v>17293.56094722222</v>
+        <v>102604.6940750001</v>
       </c>
       <c r="M90" s="4">
         <v>126991.62</v>
@@ -4744,7 +4753,7 @@
         <v>101</v>
       </c>
       <c r="B91" s="5">
-        <v>1.699588805649975</v>
+        <v>15.81320944559354</v>
       </c>
       <c r="C91" s="5">
         <v>21.19169119427137</v>
@@ -4753,7 +4762,7 @@
         <v>19.73161786868125</v>
       </c>
       <c r="E91" s="5">
-        <v>2.488774830823794</v>
+        <v>17.12836268378556</v>
       </c>
       <c r="F91" s="5">
         <v>20.05188399028683</v>
@@ -4765,7 +4774,7 @@
         <v>20.42501910458617</v>
       </c>
       <c r="I91" s="5">
-        <v>3.437375092592217</v>
+        <v>16.18924387153773</v>
       </c>
       <c r="J91" s="5">
         <v>15.7610648935347</v>
@@ -4774,7 +4783,7 @@
         <v>17.39619994397383</v>
       </c>
       <c r="L91" s="5">
-        <v>4.134458605442886</v>
+        <v>24.53022033298229</v>
       </c>
       <c r="M91" s="5">
         <v>19.72188321812301</v>
@@ -4832,7 +4841,7 @@
         <v>103</v>
       </c>
       <c r="B93" s="4">
-        <v>0</v>
+        <v>242.6315888888889</v>
       </c>
       <c r="C93" s="4">
         <v>321.5</v>
@@ -4841,7 +4850,7 @@
         <v>428.52</v>
       </c>
       <c r="E93" s="4">
-        <v>124.0256444444444</v>
+        <v>605.1745666666666</v>
       </c>
       <c r="F93" s="4">
         <v>2499.65</v>
@@ -4853,7 +4862,7 @@
         <v>3009.84</v>
       </c>
       <c r="I93" s="4">
-        <v>124.0256444444444</v>
+        <v>1620.561888888889</v>
       </c>
       <c r="J93" s="4">
         <v>2287.1</v>
@@ -4862,7 +4871,7 @@
         <v>2465.82</v>
       </c>
       <c r="L93" s="4">
-        <v>576.8153222222221</v>
+        <v>11901.73332777779</v>
       </c>
       <c r="M93" s="4">
         <v>18789</v>
@@ -4876,7 +4885,7 @@
         <v>104</v>
       </c>
       <c r="B94" s="5">
-        <v>0</v>
+        <v>12.88126931879852</v>
       </c>
       <c r="C94" s="5">
         <v>15.02392612807955</v>
@@ -4885,7 +4894,7 @@
         <v>26.58164246413042</v>
       </c>
       <c r="E94" s="5">
-        <v>2.758632722728979</v>
+        <v>13.46055785517652</v>
       </c>
       <c r="F94" s="5">
         <v>14.43398443567633</v>
@@ -4897,7 +4906,7 @@
         <v>23.6996768483581</v>
       </c>
       <c r="I94" s="5">
-        <v>0.5748874540275259</v>
+        <v>7.511677948302757</v>
       </c>
       <c r="J94" s="5">
         <v>10.3133228145347</v>
@@ -4906,7 +4915,7 @@
         <v>10.24124332619661</v>
       </c>
       <c r="L94" s="5">
-        <v>0.5430144637984963</v>
+        <v>11.20430247302984</v>
       </c>
       <c r="M94" s="5">
         <v>18.18476041778977</v>
@@ -4964,7 +4973,7 @@
         <v>106</v>
       </c>
       <c r="B96" s="4">
-        <v>0</v>
+        <v>201.2</v>
       </c>
       <c r="C96" s="4">
         <v>201.25</v>
@@ -4973,7 +4982,7 @@
         <v>195.88</v>
       </c>
       <c r="E96" s="4">
-        <v>0</v>
+        <v>402.4</v>
       </c>
       <c r="F96" s="4">
         <v>1408.75</v>
@@ -4985,7 +4994,7 @@
         <v>1597.96</v>
       </c>
       <c r="I96" s="4">
-        <v>0</v>
+        <v>1207.2</v>
       </c>
       <c r="J96" s="4">
         <v>1207.5</v>
@@ -4994,7 +5003,7 @@
         <v>1175.28</v>
       </c>
       <c r="L96" s="4">
-        <v>0</v>
+        <v>13480.4</v>
       </c>
       <c r="M96" s="4">
         <v>13483.75</v>
@@ -5038,7 +5047,7 @@
         <v>9.794</v>
       </c>
       <c r="L97" s="5">
-        <v>0</v>
+        <v>1675.749589776739</v>
       </c>
       <c r="M97" s="5">
         <v>31.35755813953488</v>
@@ -5096,7 +5105,7 @@
         <v>109</v>
       </c>
       <c r="B99" s="4">
-        <v>0</v>
+        <v>594.23</v>
       </c>
       <c r="C99" s="4">
         <v>594.37</v>
@@ -5105,7 +5114,7 @@
         <v>578.51</v>
       </c>
       <c r="E99" s="4">
-        <v>0</v>
+        <v>1188.46</v>
       </c>
       <c r="F99" s="4">
         <v>4160.59</v>
@@ -5117,7 +5126,7 @@
         <v>4049.57</v>
       </c>
       <c r="I99" s="4">
-        <v>0</v>
+        <v>3565.38</v>
       </c>
       <c r="J99" s="4">
         <v>3566.22</v>
@@ -5126,7 +5135,7 @@
         <v>3471.06</v>
       </c>
       <c r="L99" s="4">
-        <v>0</v>
+        <v>41198.453</v>
       </c>
       <c r="M99" s="4">
         <v>39822.79</v>
@@ -5258,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="L102" s="4">
-        <v>0</v>
+        <v>62.8375</v>
       </c>
       <c r="M102" s="4">
         <v>0</v>
@@ -5381,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="4">
-        <v>0</v>
+        <v>83.14458333333333</v>
       </c>
       <c r="J105" s="4">
         <v>0</v>
@@ -5390,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="L105" s="4">
-        <v>0</v>
+        <v>676.4372222222222</v>
       </c>
       <c r="M105" s="4">
         <v>0</v>
@@ -5492,7 +5501,7 @@
         <v>118</v>
       </c>
       <c r="B108" s="4">
-        <v>30.06666666666666</v>
+        <v>1031.440766666667</v>
       </c>
       <c r="C108" s="4">
         <v>1657.84</v>
@@ -5501,7 +5510,7 @@
         <v>1774.9</v>
       </c>
       <c r="E108" s="4">
-        <v>78.9111111111111</v>
+        <v>2171.839816666667</v>
       </c>
       <c r="F108" s="4">
         <v>11965.22</v>
@@ -5513,7 +5522,7 @@
         <v>14731.36</v>
       </c>
       <c r="I108" s="4">
-        <v>130.9777777777778</v>
+        <v>7226.66703888889</v>
       </c>
       <c r="J108" s="4">
         <v>10480.42</v>
@@ -5522,7 +5531,7 @@
         <v>11854</v>
       </c>
       <c r="L108" s="4">
-        <v>968.9200000000001</v>
+        <v>82489.16163611111</v>
       </c>
       <c r="M108" s="4">
         <v>104314.74</v>
@@ -5566,7 +5575,7 @@
         <v>3.260070845349241</v>
       </c>
       <c r="L109" s="5">
-        <v>156.0810593124779</v>
+        <v>13287.98634558315</v>
       </c>
       <c r="M109" s="5">
         <v>5.243680046600329</v>
@@ -5624,7 +5633,7 @@
         <v>121</v>
       </c>
       <c r="B111" s="4">
-        <v>0</v>
+        <v>729.2868055555555</v>
       </c>
       <c r="C111" s="4">
         <v>703.6900000000001</v>
@@ -5633,7 +5642,7 @@
         <v>568.38</v>
       </c>
       <c r="E111" s="4">
-        <v>0</v>
+        <v>1237.076744444444</v>
       </c>
       <c r="F111" s="4">
         <v>4008.69</v>
@@ -5645,7 +5654,7 @@
         <v>4585.84</v>
       </c>
       <c r="I111" s="4">
-        <v>0</v>
+        <v>3727.835786111111</v>
       </c>
       <c r="J111" s="4">
         <v>3465</v>
@@ -5654,7 +5663,7 @@
         <v>4133.15</v>
       </c>
       <c r="L111" s="4">
-        <v>0</v>
+        <v>29789.74147222221</v>
       </c>
       <c r="M111" s="4">
         <v>32561.11</v>
@@ -5756,7 +5765,7 @@
         <v>124</v>
       </c>
       <c r="B114" s="4">
-        <v>0</v>
+        <v>1432.93045</v>
       </c>
       <c r="C114" s="4">
         <v>495.21</v>
@@ -5765,7 +5774,7 @@
         <v>1448.74</v>
       </c>
       <c r="E114" s="4">
-        <v>0</v>
+        <v>2663.45045</v>
       </c>
       <c r="F114" s="4">
         <v>3103.91</v>
@@ -5777,7 +5786,7 @@
         <v>9829.040000000001</v>
       </c>
       <c r="I114" s="4">
-        <v>0</v>
+        <v>7866.250083333333</v>
       </c>
       <c r="J114" s="4">
         <v>2608.7</v>
@@ -5786,7 +5795,7 @@
         <v>8239.4</v>
       </c>
       <c r="L114" s="4">
-        <v>0</v>
+        <v>90699.90947222222</v>
       </c>
       <c r="M114" s="4">
         <v>29553.47</v>
@@ -5888,7 +5897,7 @@
         <v>127</v>
       </c>
       <c r="B117" s="4">
-        <v>0</v>
+        <v>368.46</v>
       </c>
       <c r="C117" s="4">
         <v>1190.63</v>
@@ -5897,7 +5906,7 @@
         <v>354.62</v>
       </c>
       <c r="E117" s="4">
-        <v>0</v>
+        <v>736.92</v>
       </c>
       <c r="F117" s="4">
         <v>8334.41</v>
@@ -5909,7 +5918,7 @@
         <v>2482.34</v>
       </c>
       <c r="I117" s="4">
-        <v>0</v>
+        <v>2210.76</v>
       </c>
       <c r="J117" s="4">
         <v>7143.78</v>
@@ -5918,7 +5927,7 @@
         <v>2127.72</v>
       </c>
       <c r="L117" s="4">
-        <v>0</v>
+        <v>24686.82</v>
       </c>
       <c r="M117" s="4">
         <v>79772.21000000001</v>
@@ -6020,7 +6029,7 @@
         <v>130</v>
       </c>
       <c r="B120" s="4">
-        <v>0</v>
+        <v>389.08</v>
       </c>
       <c r="C120" s="4">
         <v>391.37</v>
@@ -6029,7 +6038,7 @@
         <v>647.33</v>
       </c>
       <c r="E120" s="4">
-        <v>0</v>
+        <v>778.16</v>
       </c>
       <c r="F120" s="4">
         <v>2739.59</v>
@@ -6041,7 +6050,7 @@
         <v>3837.4</v>
       </c>
       <c r="I120" s="4">
-        <v>0</v>
+        <v>2334.48</v>
       </c>
       <c r="J120" s="4">
         <v>2348.22</v>
@@ -6050,7 +6059,7 @@
         <v>3050.02</v>
       </c>
       <c r="L120" s="4">
-        <v>0</v>
+        <v>26255.29333333333</v>
       </c>
       <c r="M120" s="4">
         <v>26221.79</v>
@@ -6064,7 +6073,7 @@
         <v>131</v>
       </c>
       <c r="B121" s="5">
-        <v>0</v>
+        <v>52.57837837837837</v>
       </c>
       <c r="C121" s="5">
         <v>36.25474756831867</v>
@@ -6073,7 +6082,7 @@
         <v>359.6277777777778</v>
       </c>
       <c r="E121" s="5">
-        <v>0</v>
+        <v>64.31074380165289</v>
       </c>
       <c r="F121" s="5">
         <v>32.84761939018981</v>
@@ -6085,7 +6094,7 @@
         <v>284.2518518518518</v>
       </c>
       <c r="I121" s="5">
-        <v>0</v>
+        <v>41.17248677248677</v>
       </c>
       <c r="J121" s="5">
         <v>21.60136881709549</v>
@@ -6094,7 +6103,7 @@
         <v>130.342735042735</v>
       </c>
       <c r="L121" s="5">
-        <v>0</v>
+        <v>108.0987445918637</v>
       </c>
       <c r="M121" s="5">
         <v>54.67064332655036</v>
@@ -6284,7 +6293,7 @@
         <v>136</v>
       </c>
       <c r="B126" s="4">
-        <v>0</v>
+        <v>180.48</v>
       </c>
       <c r="C126" s="4">
         <v>180</v>
@@ -6293,7 +6302,7 @@
         <v>160.51</v>
       </c>
       <c r="E126" s="4">
-        <v>0</v>
+        <v>360.875</v>
       </c>
       <c r="F126" s="4">
         <v>1322.8</v>
@@ -6305,7 +6314,7 @@
         <v>934.36</v>
       </c>
       <c r="I126" s="4">
-        <v>0</v>
+        <v>991.7322222222222</v>
       </c>
       <c r="J126" s="4">
         <v>1127.1</v>
@@ -6314,7 +6323,7 @@
         <v>1022.17</v>
       </c>
       <c r="L126" s="4">
-        <v>3617.06645</v>
+        <v>9985.534783333331</v>
       </c>
       <c r="M126" s="4">
         <v>12640.9</v>
@@ -6416,7 +6425,7 @@
         <v>139</v>
       </c>
       <c r="B129" s="4">
-        <v>0</v>
+        <v>1091.545</v>
       </c>
       <c r="C129" s="4">
         <v>1050.69</v>
@@ -6425,7 +6434,7 @@
         <v>571.9</v>
       </c>
       <c r="E129" s="4">
-        <v>0</v>
+        <v>2237.136944444444</v>
       </c>
       <c r="F129" s="4">
         <v>7950.03</v>
@@ -6437,7 +6446,7 @@
         <v>4586.44</v>
       </c>
       <c r="I129" s="4">
-        <v>0</v>
+        <v>6606.639744444445</v>
       </c>
       <c r="J129" s="4">
         <v>6648.54</v>
@@ -6446,7 +6455,7 @@
         <v>4222.83</v>
       </c>
       <c r="L129" s="4">
-        <v>0</v>
+        <v>70639.25962222221</v>
       </c>
       <c r="M129" s="4">
         <v>68645.83</v>
@@ -6548,7 +6557,7 @@
         <v>142</v>
       </c>
       <c r="B132" s="4">
-        <v>226.1758333333333</v>
+        <v>1566.600005555556</v>
       </c>
       <c r="C132" s="4">
         <v>1626.1</v>
@@ -6557,7 +6566,7 @@
         <v>1837.76</v>
       </c>
       <c r="E132" s="4">
-        <v>344.2591666666667</v>
+        <v>3084.715750000001</v>
       </c>
       <c r="F132" s="4">
         <v>12779.7</v>
@@ -6569,7 +6578,7 @@
         <v>15855.89</v>
       </c>
       <c r="I132" s="4">
-        <v>1690.519444444444</v>
+        <v>12556.75846666666</v>
       </c>
       <c r="J132" s="4">
         <v>14616.6</v>
@@ -6578,7 +6587,7 @@
         <v>15619.67</v>
       </c>
       <c r="L132" s="4">
-        <v>10813.88347222223</v>
+        <v>76240.8699722223</v>
       </c>
       <c r="M132" s="4">
         <v>89805.39999999999</v>
@@ -6710,7 +6719,7 @@
         <v>436.25</v>
       </c>
       <c r="L135" s="4">
-        <v>0</v>
+        <v>716.1311111111111</v>
       </c>
       <c r="M135" s="4">
         <v>0</v>
@@ -6812,7 +6821,7 @@
         <v>148</v>
       </c>
       <c r="B138" s="4">
-        <v>0</v>
+        <v>880.5443055555555</v>
       </c>
       <c r="C138" s="4">
         <v>790.25</v>
@@ -6821,7 +6830,7 @@
         <v>1051.27</v>
       </c>
       <c r="E138" s="4">
-        <v>0</v>
+        <v>1808.058333333333</v>
       </c>
       <c r="F138" s="4">
         <v>6945.5</v>
@@ -6833,7 +6842,7 @@
         <v>8301.610000000001</v>
       </c>
       <c r="I138" s="4">
-        <v>456.1620833333333</v>
+        <v>8572.762222222222</v>
       </c>
       <c r="J138" s="4">
         <v>8765.5</v>
@@ -6842,7 +6851,7 @@
         <v>11582.05</v>
       </c>
       <c r="L138" s="4">
-        <v>2822.435000000001</v>
+        <v>43020.14499999998</v>
       </c>
       <c r="M138" s="4">
         <v>54886</v>
@@ -6877,7 +6886,7 @@
         <v>372.8513554785046</v>
       </c>
       <c r="I139" s="5">
-        <v>380.1350694444444</v>
+        <v>7143.968518518518</v>
       </c>
       <c r="J139" s="5">
         <v>169.228600994656</v>
@@ -6886,7 +6895,7 @@
         <v>453.0396789385571</v>
       </c>
       <c r="L139" s="5">
-        <v>940.811666666667</v>
+        <v>14340.04833333333</v>
       </c>
       <c r="M139" s="5">
         <v>126.059491370646</v>
@@ -7208,7 +7217,7 @@
         <v>157</v>
       </c>
       <c r="B147" s="4">
-        <v>0</v>
+        <v>598.8556527777778</v>
       </c>
       <c r="C147" s="4">
         <v>642.47</v>
@@ -7217,7 +7226,7 @@
         <v>223.76</v>
       </c>
       <c r="E147" s="4">
-        <v>0</v>
+        <v>1357.089194444444</v>
       </c>
       <c r="F147" s="4">
         <v>5114.06</v>
@@ -7229,7 +7238,7 @@
         <v>2640.92</v>
       </c>
       <c r="I147" s="4">
-        <v>0</v>
+        <v>4498.140805555556</v>
       </c>
       <c r="J147" s="4">
         <v>4277.54</v>
@@ -7238,7 +7247,7 @@
         <v>1960.79</v>
       </c>
       <c r="L147" s="4">
-        <v>0</v>
+        <v>49543.26195277776</v>
       </c>
       <c r="M147" s="4">
         <v>48631.04</v>
@@ -7472,7 +7481,7 @@
         <v>163</v>
       </c>
       <c r="B153" s="4">
-        <v>0</v>
+        <v>771.5232888888888</v>
       </c>
       <c r="C153" s="4">
         <v>700.16</v>
@@ -7481,7 +7490,7 @@
         <v>622.3099999999999</v>
       </c>
       <c r="E153" s="4">
-        <v>0</v>
+        <v>1541.6788</v>
       </c>
       <c r="F153" s="4">
         <v>5147.08</v>
@@ -7493,7 +7502,7 @@
         <v>4308.91</v>
       </c>
       <c r="I153" s="4">
-        <v>446.5</v>
+        <v>4533.630433333334</v>
       </c>
       <c r="J153" s="4">
         <v>4446.92</v>
@@ -7502,7 +7511,7 @@
         <v>3772.42</v>
       </c>
       <c r="L153" s="4">
-        <v>1588.716666666667</v>
+        <v>48035.15091666667</v>
       </c>
       <c r="M153" s="4">
         <v>47450.32</v>
@@ -7604,7 +7613,7 @@
         <v>166</v>
       </c>
       <c r="B156" s="4">
-        <v>0</v>
+        <v>999.45</v>
       </c>
       <c r="C156" s="4">
         <v>1260.41</v>
@@ -7613,7 +7622,7 @@
         <v>1142.01</v>
       </c>
       <c r="E156" s="4">
-        <v>0</v>
+        <v>1998.9</v>
       </c>
       <c r="F156" s="4">
         <v>8662.870000000001</v>
@@ -7625,7 +7634,7 @@
         <v>7994.07</v>
       </c>
       <c r="I156" s="4">
-        <v>0</v>
+        <v>5996.7</v>
       </c>
       <c r="J156" s="4">
         <v>7402.46</v>
@@ -7634,7 +7643,7 @@
         <v>6852.06</v>
       </c>
       <c r="L156" s="4">
-        <v>0</v>
+        <v>66963.14999999999</v>
       </c>
       <c r="M156" s="4">
         <v>82847.47</v>
@@ -7736,7 +7745,7 @@
         <v>169</v>
       </c>
       <c r="B159" s="4">
-        <v>0</v>
+        <v>625.4555555555556</v>
       </c>
       <c r="C159" s="4">
         <v>988.51</v>
@@ -7745,7 +7754,7 @@
         <v>642.28</v>
       </c>
       <c r="E159" s="4">
-        <v>0</v>
+        <v>1114.461388888889</v>
       </c>
       <c r="F159" s="4">
         <v>5645.97</v>
@@ -7757,7 +7766,7 @@
         <v>4527.49</v>
       </c>
       <c r="I159" s="4">
-        <v>0</v>
+        <v>3428.288611111112</v>
       </c>
       <c r="J159" s="4">
         <v>4857.46</v>
@@ -7766,7 +7775,7 @@
         <v>4079.69</v>
       </c>
       <c r="L159" s="4">
-        <v>0</v>
+        <v>36508.66722222223</v>
       </c>
       <c r="M159" s="4">
         <v>54438.17</v>
@@ -7868,7 +7877,7 @@
         <v>172</v>
       </c>
       <c r="B162" s="4">
-        <v>0</v>
+        <v>398.52</v>
       </c>
       <c r="C162" s="4">
         <v>227.21</v>
@@ -7877,7 +7886,7 @@
         <v>225.28</v>
       </c>
       <c r="E162" s="4">
-        <v>0</v>
+        <v>797.04</v>
       </c>
       <c r="F162" s="4">
         <v>1590.47</v>
@@ -7889,7 +7898,7 @@
         <v>1576.96</v>
       </c>
       <c r="I162" s="4">
-        <v>0</v>
+        <v>2391.12</v>
       </c>
       <c r="J162" s="4">
         <v>1363.26</v>
@@ -7898,7 +7907,7 @@
         <v>1351.68</v>
       </c>
       <c r="L162" s="4">
-        <v>0</v>
+        <v>26700.84</v>
       </c>
       <c r="M162" s="4">
         <v>15223.07</v>
@@ -8000,7 +8009,7 @@
         <v>175</v>
       </c>
       <c r="B165" s="4">
-        <v>0</v>
+        <v>849.5524138888889</v>
       </c>
       <c r="C165" s="4">
         <v>849.62</v>
@@ -8009,7 +8018,7 @@
         <v>333.12</v>
       </c>
       <c r="E165" s="4">
-        <v>0</v>
+        <v>1703.263452777778</v>
       </c>
       <c r="F165" s="4">
         <v>5634.22</v>
@@ -8021,7 +8030,7 @@
         <v>1822.26</v>
       </c>
       <c r="I165" s="4">
-        <v>0</v>
+        <v>4791.158141666667</v>
       </c>
       <c r="J165" s="4">
         <v>4784.6</v>
@@ -8030,7 +8039,7 @@
         <v>1509</v>
       </c>
       <c r="L165" s="4">
-        <v>0</v>
+        <v>54073.49543333334</v>
       </c>
       <c r="M165" s="4">
         <v>53793.34</v>
@@ -8132,7 +8141,7 @@
         <v>178</v>
       </c>
       <c r="B168" s="4">
-        <v>0</v>
+        <v>175.48</v>
       </c>
       <c r="C168" s="4">
         <v>0</v>
@@ -8141,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="E168" s="4">
-        <v>0</v>
+        <v>350.96</v>
       </c>
       <c r="F168" s="4">
         <v>0</v>
@@ -8153,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="I168" s="4">
-        <v>138.67</v>
+        <v>1052.88</v>
       </c>
       <c r="J168" s="4">
         <v>0</v>
@@ -8162,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="4">
-        <v>418.925</v>
+        <v>11757.16</v>
       </c>
       <c r="M168" s="4">
         <v>0</v>
@@ -8256,7 +8265,7 @@
         <v>0</v>
       </c>
       <c r="N170" s="4">
-        <v>1364.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:14">
@@ -8285,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="I171" s="4">
-        <v>95.93000000000001</v>
+        <v>138.67</v>
       </c>
       <c r="J171" s="4">
         <v>0</v>
@@ -8294,13 +8303,13 @@
         <v>0</v>
       </c>
       <c r="L171" s="4">
-        <v>203.83</v>
+        <v>418.925</v>
       </c>
       <c r="M171" s="4">
         <v>0</v>
       </c>
       <c r="N171" s="4">
-        <v>228.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:14">
@@ -8344,139 +8353,139 @@
         <v>0</v>
       </c>
       <c r="N172" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14">
+      <c r="A173" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B173" s="4">
+        <v>0</v>
+      </c>
+      <c r="C173" s="4">
+        <v>0</v>
+      </c>
+      <c r="D173" s="4">
+        <v>0</v>
+      </c>
+      <c r="E173" s="4">
+        <v>0</v>
+      </c>
+      <c r="F173" s="4">
+        <v>0</v>
+      </c>
+      <c r="G173" s="4">
+        <v>0</v>
+      </c>
+      <c r="H173" s="4">
+        <v>0</v>
+      </c>
+      <c r="I173" s="4">
+        <v>0</v>
+      </c>
+      <c r="J173" s="4">
+        <v>0</v>
+      </c>
+      <c r="K173" s="4">
+        <v>0</v>
+      </c>
+      <c r="L173" s="4">
+        <v>0</v>
+      </c>
+      <c r="M173" s="4">
+        <v>0</v>
+      </c>
+      <c r="N173" s="4">
+        <v>1364.14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14">
+      <c r="A174" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B174" s="4">
+        <v>0</v>
+      </c>
+      <c r="C174" s="4">
+        <v>0</v>
+      </c>
+      <c r="D174" s="4">
+        <v>0</v>
+      </c>
+      <c r="E174" s="4">
+        <v>0</v>
+      </c>
+      <c r="F174" s="4">
+        <v>0</v>
+      </c>
+      <c r="G174" s="4">
+        <v>0</v>
+      </c>
+      <c r="H174" s="4">
+        <v>0</v>
+      </c>
+      <c r="I174" s="4">
+        <v>95.93000000000001</v>
+      </c>
+      <c r="J174" s="4">
+        <v>0</v>
+      </c>
+      <c r="K174" s="4">
+        <v>0</v>
+      </c>
+      <c r="L174" s="4">
+        <v>203.83</v>
+      </c>
+      <c r="M174" s="4">
+        <v>0</v>
+      </c>
+      <c r="N174" s="4">
+        <v>228.24</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14">
+      <c r="A175" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B175" s="5">
+        <v>0</v>
+      </c>
+      <c r="C175" s="5">
+        <v>0</v>
+      </c>
+      <c r="D175" s="5">
+        <v>0</v>
+      </c>
+      <c r="E175" s="5">
+        <v>0</v>
+      </c>
+      <c r="F175" s="5">
+        <v>0</v>
+      </c>
+      <c r="G175" s="5">
+        <v>0</v>
+      </c>
+      <c r="H175" s="5">
+        <v>0</v>
+      </c>
+      <c r="I175" s="5">
+        <v>0</v>
+      </c>
+      <c r="J175" s="5">
+        <v>0</v>
+      </c>
+      <c r="K175" s="5">
+        <v>0</v>
+      </c>
+      <c r="L175" s="5">
+        <v>0</v>
+      </c>
+      <c r="M175" s="5">
+        <v>0</v>
+      </c>
+      <c r="N175" s="5">
         <v>16.73142052868474</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14">
-      <c r="A175" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B175" s="4">
-        <v>186986.29</v>
-      </c>
-      <c r="C175" s="4">
-        <v>339542.96</v>
-      </c>
-      <c r="D175" s="4">
-        <v>121909.27</v>
-      </c>
-      <c r="E175" s="4">
-        <v>415713.5099999999</v>
-      </c>
-      <c r="F175" s="4">
-        <v>2424435.539999999</v>
-      </c>
-      <c r="G175" s="4">
-        <v>385010.46</v>
-      </c>
-      <c r="H175" s="4">
-        <v>1351697.96</v>
-      </c>
-      <c r="I175" s="4">
-        <v>1731807.06</v>
-      </c>
-      <c r="J175" s="4">
-        <v>3164672.440000002</v>
-      </c>
-      <c r="K175" s="4">
-        <v>1953216.08</v>
-      </c>
-      <c r="L175" s="4">
-        <v>5820342.210000001</v>
-      </c>
-      <c r="M175" s="4">
-        <v>13394347.11</v>
-      </c>
-      <c r="N175" s="4">
-        <v>8019359.780000001</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14">
-      <c r="A176" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B176" s="4">
-        <v>2105.0342</v>
-      </c>
-      <c r="C176" s="4">
-        <v>49426.35000000001</v>
-      </c>
-      <c r="D176" s="4">
-        <v>48454.66</v>
-      </c>
-      <c r="E176" s="4">
-        <v>5035.289244444445</v>
-      </c>
-      <c r="F176" s="4">
-        <v>346487.9799999998</v>
-      </c>
-      <c r="G176" s="4">
-        <v>106075.39</v>
-      </c>
-      <c r="H176" s="4">
-        <v>366174.4500000001</v>
-      </c>
-      <c r="I176" s="4">
-        <v>20264.07165555555</v>
-      </c>
-      <c r="J176" s="4">
-        <v>348254.14</v>
-      </c>
-      <c r="K176" s="4">
-        <v>360201.51</v>
-      </c>
-      <c r="L176" s="4">
-        <v>126328.3785444444</v>
-      </c>
-      <c r="M176" s="4">
-        <v>2695102.56</v>
-      </c>
-      <c r="N176" s="4">
-        <v>2665750.81</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14">
-      <c r="A177" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B177" s="5">
-        <v>1.125769274314175</v>
-      </c>
-      <c r="C177" s="5">
-        <v>14.55672943417823</v>
-      </c>
-      <c r="D177" s="5">
-        <v>39.74649343729152</v>
-      </c>
-      <c r="E177" s="5">
-        <v>1.21124022273042</v>
-      </c>
-      <c r="F177" s="5">
-        <v>14.29149071127706</v>
-      </c>
-      <c r="G177" s="5">
-        <v>27.55130081400905</v>
-      </c>
-      <c r="H177" s="5">
-        <v>27.08996098507097</v>
-      </c>
-      <c r="I177" s="5">
-        <v>1.170111389634568</v>
-      </c>
-      <c r="J177" s="5">
-        <v>11.00442926093165</v>
-      </c>
-      <c r="K177" s="5">
-        <v>18.44145733225788</v>
-      </c>
-      <c r="L177" s="5">
-        <v>2.170463075648681</v>
-      </c>
-      <c r="M177" s="5">
-        <v>20.1211939474667</v>
-      </c>
-      <c r="N177" s="5">
-        <v>33.24144175010439</v>
       </c>
     </row>
     <row r="178" spans="1:14">
@@ -8484,42 +8493,174 @@
         <v>186</v>
       </c>
       <c r="B178" s="4">
-        <v>184881.2558</v>
+        <v>186986.29</v>
       </c>
       <c r="C178" s="4">
+        <v>339542.96</v>
+      </c>
+      <c r="D178" s="4">
+        <v>121909.27</v>
+      </c>
+      <c r="E178" s="4">
+        <v>415713.5099999999</v>
+      </c>
+      <c r="F178" s="4">
+        <v>2424435.539999999</v>
+      </c>
+      <c r="G178" s="4">
+        <v>385010.46</v>
+      </c>
+      <c r="H178" s="4">
+        <v>1351697.96</v>
+      </c>
+      <c r="I178" s="4">
+        <v>1731807.06</v>
+      </c>
+      <c r="J178" s="4">
+        <v>3164672.440000002</v>
+      </c>
+      <c r="K178" s="4">
+        <v>1953216.08</v>
+      </c>
+      <c r="L178" s="4">
+        <v>5820342.210000001</v>
+      </c>
+      <c r="M178" s="4">
+        <v>13394347.11</v>
+      </c>
+      <c r="N178" s="4">
+        <v>8019359.780000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14">
+      <c r="A179" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B179" s="4">
+        <v>42350.34721666667</v>
+      </c>
+      <c r="C179" s="4">
+        <v>49426.35000000001</v>
+      </c>
+      <c r="D179" s="4">
+        <v>48454.66</v>
+      </c>
+      <c r="E179" s="4">
+        <v>89911.73748888889</v>
+      </c>
+      <c r="F179" s="4">
+        <v>346487.9799999998</v>
+      </c>
+      <c r="G179" s="4">
+        <v>106075.39</v>
+      </c>
+      <c r="H179" s="4">
+        <v>366174.4500000001</v>
+      </c>
+      <c r="I179" s="4">
+        <v>300921.5228083335</v>
+      </c>
+      <c r="J179" s="4">
+        <v>348254.14</v>
+      </c>
+      <c r="K179" s="4">
+        <v>360201.51</v>
+      </c>
+      <c r="L179" s="4">
+        <v>2439966.692363888</v>
+      </c>
+      <c r="M179" s="4">
+        <v>2695102.56</v>
+      </c>
+      <c r="N179" s="4">
+        <v>2665750.81</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14">
+      <c r="A180" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B180" s="5">
+        <v>22.6489050168687</v>
+      </c>
+      <c r="C180" s="5">
+        <v>14.55672943417823</v>
+      </c>
+      <c r="D180" s="5">
+        <v>39.74649343729152</v>
+      </c>
+      <c r="E180" s="5">
+        <v>21.62829336214955</v>
+      </c>
+      <c r="F180" s="5">
+        <v>14.29149071127706</v>
+      </c>
+      <c r="G180" s="5">
+        <v>27.55130081400905</v>
+      </c>
+      <c r="H180" s="5">
+        <v>27.08996098507097</v>
+      </c>
+      <c r="I180" s="5">
+        <v>17.37615752694376</v>
+      </c>
+      <c r="J180" s="5">
+        <v>11.00442926093165</v>
+      </c>
+      <c r="K180" s="5">
+        <v>18.44145733225788</v>
+      </c>
+      <c r="L180" s="5">
+        <v>41.92136139644422</v>
+      </c>
+      <c r="M180" s="5">
+        <v>20.1211939474667</v>
+      </c>
+      <c r="N180" s="5">
+        <v>33.24144175010439</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14">
+      <c r="A181" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B181" s="4">
+        <v>144635.9427833334</v>
+      </c>
+      <c r="C181" s="4">
         <v>290116.61</v>
       </c>
-      <c r="D178" s="4">
+      <c r="D181" s="4">
         <v>73454.60999999999</v>
       </c>
-      <c r="E178" s="4">
-        <v>410678.2207555554</v>
-      </c>
-      <c r="F178" s="4">
+      <c r="E181" s="4">
+        <v>325801.772511111</v>
+      </c>
+      <c r="F181" s="4">
         <v>2077947.559999999</v>
       </c>
-      <c r="G178" s="4">
+      <c r="G181" s="4">
         <v>278935.0699999999</v>
       </c>
-      <c r="H178" s="4">
+      <c r="H181" s="4">
         <v>985523.5099999998</v>
       </c>
-      <c r="I178" s="4">
-        <v>1711542.988344444</v>
-      </c>
-      <c r="J178" s="4">
+      <c r="I181" s="4">
+        <v>1430885.537191666</v>
+      </c>
+      <c r="J181" s="4">
         <v>2816418.300000002</v>
       </c>
-      <c r="K178" s="4">
+      <c r="K181" s="4">
         <v>1593014.57</v>
       </c>
-      <c r="L178" s="4">
-        <v>5694013.831455557</v>
-      </c>
-      <c r="M178" s="4">
+      <c r="L181" s="4">
+        <v>3380375.517636112</v>
+      </c>
+      <c r="M181" s="4">
         <v>10699244.55</v>
       </c>
-      <c r="N178" s="4">
+      <c r="N181" s="4">
         <v>5353608.970000002</v>
       </c>
     </row>
